--- a/output/pdf_financials_xlsx/MJRX.xlsx
+++ b/output/pdf_financials_xlsx/MJRX.xlsx
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.831776</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.831776</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.831776</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.831776</v>
       </c>
     </row>
     <row r="93">
@@ -3886,7 +3886,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>6.831776</v>
       </c>

--- a/output/pdf_financials_xlsx/MJRX.xlsx
+++ b/output/pdf_financials_xlsx/MJRX.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>-1.625195</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.078204</v>
+        <v>-1.078218</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.265375</v>
@@ -1008,7 +1008,7 @@
         <v>-1.625195</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.078204</v>
+        <v>-1.078218</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.265375</v>
@@ -1027,7 +1027,7 @@
         <v>-1580.098975246466</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1299.620312669503</v>
+        <v>-1299.63718766197</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-2648.835067300245</v>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.496692</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.214338</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009191</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.050485</v>
       </c>
     </row>
     <row r="35">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.496692</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.214338</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009191</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.050485</v>
       </c>
     </row>
     <row r="37">
@@ -1351,16 +1351,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.567432</v>
+        <v>0.07074</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.23131</v>
+        <v>0.016972</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.020839</v>
+        <v>0.011648</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.063745</v>
+        <v>0.01326</v>
       </c>
     </row>
     <row r="49">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">

--- a/output/pdf_financials_xlsx/MJRX.xlsx
+++ b/output/pdf_financials_xlsx/MJRX.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.019074</v>
+        <v>0.257465</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.229885</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.473691</v>
+        <v>0.712082</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.823056</v>
@@ -5552,7 +5552,11 @@
           <t>Management and director fees (note 11)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>0.238391</v>
       </c>
